--- a/docs/d/129/inyear.xlsx
+++ b/docs/d/129/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 91 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 90 clubs short</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3077,8 +3077,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -7131,13 +7131,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>0</v>
@@ -12448,7 +12448,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q115" s="10" t="n">
         <v>2</v>
@@ -13419,7 +13419,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>

--- a/docs/d/129/inyear.xlsx
+++ b/docs/d/129/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,11 @@
       <c r="AB3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2783,7 +2787,11 @@
       <c r="AB20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2884,7 +2892,11 @@
       <c r="AB21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2985,7 +2997,11 @@
       <c r="AB22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AC22" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3708,7 +3724,11 @@
       <c r="AB29" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -4833,7 +4853,11 @@
       <c r="AB40" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC40" s="4" t="inlineStr"/>
+      <c r="AC40" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -4934,7 +4958,11 @@
       <c r="AB41" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC41" s="4" t="inlineStr"/>
+      <c r="AC41" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -9745,7 +9773,11 @@
       <c r="AB88" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC88" s="4" t="inlineStr"/>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -11262,7 +11294,11 @@
       <c r="AB103" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC103" s="4" t="inlineStr"/>
+      <c r="AC103" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -12486,7 +12522,11 @@
       <c r="AB115" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC115" s="4" t="inlineStr"/>
+      <c r="AC115" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -12894,7 +12934,11 @@
       <c r="AB119" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC119" s="4" t="inlineStr"/>
+      <c r="AC119" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -12995,7 +13039,11 @@
       <c r="AB120" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC120" s="4" t="inlineStr"/>
+      <c r="AC120" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">

--- a/docs/d/129/inyear.xlsx
+++ b/docs/d/129/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 90 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 85 clubs short</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2883,8 +2883,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="P41" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q41" s="9" t="n">
         <v>1</v>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76" s="9" t="n">
         <v>0</v>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9764,8 +9764,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11903,8 +11903,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -12004,8 +12004,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="9" t="n">
         <v>0</v>
@@ -12443,7 +12443,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12513,8 +12513,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12806,7 +12806,7 @@
         <v>1</v>
       </c>
       <c r="U118" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V118" s="9" t="n">
         <v>0</v>
@@ -12902,7 +12902,7 @@
         <v>2</v>
       </c>
       <c r="R119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S119" s="10" t="n">
         <v>2</v>
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13006,8 +13006,8 @@
       <c r="Q120" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R120" s="9" t="n">
-        <v>1</v>
+      <c r="R120" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S120" s="9" t="n">
         <v>1</v>
@@ -13467,7 +13467,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -13929,7 +13929,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14061,7 +14061,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14094,7 +14094,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -14127,7 +14127,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>3.17</v>
+        <v>3.33</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>

--- a/docs/d/129/inyear.xlsx
+++ b/docs/d/129/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 85 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 57 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>4</v>
       </c>
       <c r="W3" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X3" s="10" t="n">
         <v>4</v>
@@ -1023,8 +1023,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1431,8 +1431,8 @@
       <c r="Y7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="9" t="n">
-        <v>0</v>
+      <c r="Z7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA7" s="10" t="n">
         <v>1</v>
@@ -1526,8 +1526,8 @@
       <c r="W8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X8" s="9" t="n">
-        <v>3</v>
+      <c r="X8" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y8" s="9" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1637,8 +1637,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1839,8 +1839,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1929,8 +1929,8 @@
       <c r="T12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U12" s="9" t="n">
-        <v>0</v>
+      <c r="U12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V12" s="9" t="n">
         <v>1</v>
@@ -1944,8 +1944,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2229,8 +2229,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P15" s="9" t="n">
-        <v>3</v>
+      <c r="P15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>1</v>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>0</v>
@@ -2364,8 +2364,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2568,8 +2568,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2673,8 +2673,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>0</v>
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3793,8 +3793,8 @@
       <c r="P30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="9" t="n">
-        <v>0</v>
+      <c r="Q30" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R30" s="9" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="P31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>0</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4131,8 +4131,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="P36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="9" t="n">
         <v>0</v>
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4519,8 +4519,8 @@
       <c r="S37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T37" s="9" t="n">
-        <v>0</v>
+      <c r="T37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U37" s="9" t="n">
         <v>0</v>
@@ -4537,8 +4537,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4844,8 +4844,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5103,17 +5103,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M43" s="7" t="n">
@@ -5147,11 +5147,11 @@
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" s="9" t="n">
-        <v>0</v>
+      <c r="V43" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>4</v>
@@ -5159,8 +5159,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5204,13 +5204,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5260,8 +5260,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5365,8 +5365,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5575,8 +5575,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5606,7 +5606,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5647,19 +5647,19 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U48" s="9" t="n">
         <v>0</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5781,8 +5781,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q56" s="9" t="n">
         <v>0</v>
@@ -6500,8 +6500,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6807,8 +6807,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>7</v>
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7159,17 +7159,17 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L63" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M63" s="7" t="n">
@@ -7203,11 +7203,11 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="9" t="n">
-        <v>3</v>
+      <c r="V63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>7</v>
@@ -7215,8 +7215,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>1</v>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7522,8 +7522,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7930,8 +7930,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8233,8 +8233,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8338,8 +8338,8 @@
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -10550,7 +10550,7 @@
         <v>0</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11180,8 +11180,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11495,8 +11495,8 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -12035,7 +12035,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12105,8 +12105,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -12443,7 +12443,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12498,8 +12498,8 @@
       <c r="T115" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U115" s="9" t="n">
-        <v>0</v>
+      <c r="U115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V115" s="9" t="n">
         <v>0</v>
@@ -12548,7 +12548,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12612,14 +12612,14 @@
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="9" t="n">
-        <v>3</v>
+      <c r="X116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -12896,7 +12896,7 @@
         </is>
       </c>
       <c r="P119" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q119" s="10" t="n">
         <v>2</v>
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13000,8 +13000,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P120" s="9" t="n">
-        <v>3</v>
+      <c r="P120" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q120" s="10" t="n">
         <v>2</v>
@@ -13009,14 +13009,14 @@
       <c r="R120" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S120" s="9" t="n">
-        <v>1</v>
+      <c r="S120" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T120" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U120" s="9" t="n">
-        <v>0</v>
+      <c r="U120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V120" s="10" t="n">
         <v>4</v>
@@ -13335,7 +13335,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -13368,7 +13368,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13401,7 +13401,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13434,7 +13434,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13566,7 +13566,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13599,7 +13599,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13614,7 +13614,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -13632,7 +13632,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13665,7 +13665,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13731,7 +13731,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13764,7 +13764,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13779,7 +13779,7 @@
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -13797,7 +13797,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13830,7 +13830,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13995,7 +13995,7 @@
         <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14061,7 +14061,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14094,7 +14094,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -14127,7 +14127,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>3.33</v>
+        <v>3.83</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>

--- a/docs/d/129/inyear.xlsx
+++ b/docs/d/129/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/129/inyear.xlsx
+++ b/docs/d/129/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/129/inyear.xlsx
+++ b/docs/d/129/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/129/inyear.xlsx
+++ b/docs/d/129/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/129/inyear.xlsx
+++ b/docs/d/129/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 19 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 19 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 58 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 57 clubs short</t>
         </is>
       </c>
     </row>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1515,8 +1515,8 @@
       <c r="T8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U8" s="9" t="n">
-        <v>0</v>
+      <c r="U8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V8" s="9" t="n">
         <v>0</v>
@@ -1781,13 +1781,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1987,13 +1987,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>4</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>7</v>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2241,8 +2241,8 @@
       <c r="U15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="9" t="n">
-        <v>3</v>
+      <c r="V15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>4</v>
@@ -3241,13 +3241,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3383,8 +3383,8 @@
       <c r="T26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U26" s="9" t="n">
-        <v>0</v>
+      <c r="U26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V26" s="10" t="n">
         <v>4</v>
@@ -3964,13 +3964,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-18</v>
+        <v>-14</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="P34" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q34" s="9" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4279,13 +4279,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4323,11 +4323,11 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="9" t="n">
-        <v>0</v>
+      <c r="V35" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W35" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X35" s="10" t="n">
         <v>7</v>
@@ -5818,13 +5818,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -6335,13 +6335,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6949,13 +6949,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7285,8 +7285,8 @@
       <c r="P64" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q64" s="9" t="n">
-        <v>1</v>
+      <c r="Q64" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R64" s="9" t="n">
         <v>0</v>
@@ -7357,13 +7357,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>4</v>
       </c>
       <c r="W65" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X65" s="10" t="n">
         <v>7</v>
@@ -7870,13 +7870,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -8173,13 +8173,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8274,13 +8274,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -9300,13 +9300,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-23</v>
+        <v>-8</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9401,13 +9401,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10112,17 +10112,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="L92" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -10168,8 +10168,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -10213,13 +10213,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-21</v>
+        <v>-8</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -11528,17 +11528,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>50</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-50</v>
-      </c>
-      <c r="L106" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-15</v>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -11724,7 +11724,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11767,8 +11767,8 @@
       <c r="P108" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" s="9" t="n">
-        <v>1</v>
+      <c r="Q108" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
@@ -12031,7 +12031,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
@@ -12089,8 +12089,8 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>3</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -12789,7 +12789,7 @@
         <v>2</v>
       </c>
       <c r="R118" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S118" s="10" t="n">
         <v>2</v>
@@ -13667,7 +13667,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13700,7 +13700,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -13799,13 +13799,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -14063,13 +14063,13 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -14228,7 +14228,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14243,7 +14243,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -14309,7 +14309,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -14327,7 +14327,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14360,7 +14360,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>

--- a/docs/d/129/inyear.xlsx
+++ b/docs/d/129/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 19 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 19 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 57 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 57 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -903,8 +903,8 @@
       <c r="T2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U2" s="9" t="n">
-        <v>0</v>
+      <c r="U2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V2" s="9" t="n">
         <v>1</v>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1014,8 +1014,8 @@
       <c r="V3" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W3" s="9" t="n">
-        <v>3</v>
+      <c r="W3" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X3" s="10" t="n">
         <v>4</v>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>0</v>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="P13" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>1</v>
@@ -2022,14 +2022,14 @@
       <c r="R13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="9" t="n">
-        <v>1</v>
+      <c r="S13" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T13" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V13" s="10" t="n">
         <v>4</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2337,8 +2337,8 @@
       <c r="R16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S16" s="9" t="n">
-        <v>0</v>
+      <c r="S16" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T16" s="10" t="n">
         <v>1</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2445,8 +2445,8 @@
       <c r="S17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T17" s="9" t="n">
-        <v>0</v>
+      <c r="T17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U17" s="9" t="n">
         <v>0</v>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2862,8 +2862,8 @@
       <c r="T21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U21" s="9" t="n">
-        <v>0</v>
+      <c r="U21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V21" s="10" t="n">
         <v>4</v>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="P22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>0</v>
@@ -3342,17 +3342,17 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M26" s="8" t="n">
@@ -3390,7 +3390,7 @@
         <v>4</v>
       </c>
       <c r="W26" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>6</v>
@@ -3964,13 +3964,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>0</v>
@@ -4279,13 +4279,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>4</v>
       </c>
       <c r="W35" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X35" s="10" t="n">
         <v>7</v>
@@ -4378,17 +4378,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-22</v>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M36" s="8" t="n">
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4992,13 +4992,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="9" t="n">
         <v>0</v>
@@ -5804,7 +5804,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5818,13 +5818,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5845,16 +5845,16 @@
         </is>
       </c>
       <c r="P50" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q50" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="T50" s="10" t="n">
         <v>1</v>
@@ -6234,13 +6234,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6537,13 +6537,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7256,17 +7256,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L64" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q64" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64" s="9" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       <c r="T64" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U64" s="9" t="n">
-        <v>0</v>
+      <c r="U64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V64" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W64" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X64" s="10" t="n">
         <v>7</v>
@@ -7458,13 +7458,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7870,13 +7870,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8101,8 +8101,8 @@
       <c r="P72" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q72" s="9" t="n">
-        <v>1</v>
+      <c r="Q72" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9300,13 +9300,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9344,8 +9344,8 @@
       <c r="U84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="9" t="n">
-        <v>2</v>
+      <c r="V84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9805,13 +9805,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>0</v>
@@ -9853,7 +9853,7 @@
         <v>4</v>
       </c>
       <c r="W89" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X89" s="9" t="n">
         <v>0</v>
@@ -10007,13 +10007,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>4</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X91" s="10" t="n">
         <v>7</v>
@@ -10139,7 +10139,7 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" s="9" t="n">
         <v>0</v>
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" s="9" t="n">
         <v>0</v>
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10314,13 +10314,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10358,11 +10358,11 @@
       <c r="U94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="9" t="n">
-        <v>0</v>
+      <c r="V94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X94" s="10" t="n">
         <v>7</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-18</v>
+        <v>-9</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10516,13 +10516,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-12</v>
+        <v>-7</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10718,13 +10718,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10819,13 +10819,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10920,13 +10920,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11662,8 +11662,8 @@
       <c r="P107" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" s="9" t="n">
-        <v>0</v>
+      <c r="Q107" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X111" s="10" t="n">
         <v>6</v>
@@ -12756,13 +12756,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         </is>
       </c>
       <c r="P118" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q118" s="10" t="n">
         <v>2</v>
@@ -12804,7 +12804,7 @@
         <v>4</v>
       </c>
       <c r="W118" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X118" s="10" t="n">
         <v>7</v>
@@ -13096,7 +13096,7 @@
         <v>2</v>
       </c>
       <c r="R121" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S121" s="10" t="n">
         <v>2</v>
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="P122" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q122" s="10" t="n">
         <v>2</v>
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         </is>
       </c>
       <c r="P123" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q123" s="10" t="n">
         <v>2</v>
@@ -13309,13 +13309,13 @@
         <v>2</v>
       </c>
       <c r="S123" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U123" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="T123" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U123" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="V123" s="10" t="n">
         <v>4</v>
@@ -13634,13 +13634,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -13700,7 +13700,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -13733,13 +13733,13 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -13766,7 +13766,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -13814,7 +13814,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -13880,7 +13880,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -13964,7 +13964,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14063,7 +14063,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -14078,7 +14078,7 @@
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -14096,7 +14096,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14195,7 +14195,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14261,7 +14261,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14327,7 +14327,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
